--- a/docs/results/ch4_fw2_pole_geometry_summary.xlsx
+++ b/docs/results/ch4_fw2_pole_geometry_summary.xlsx
@@ -497,29 +497,29 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.004985156652160107</v>
+        <v>-0.1019152765636377</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3932387590803919</v>
+        <v>0.1914312790022934</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1294852658887813</v>
+        <v>0.01842407250193736</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.07763034899903777</v>
+        <v>-0.03645324145426942</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1515643815011876</v>
+        <v>-0.04709385690407879</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.07657599462280111</v>
+        <v>-0.02505227387401057</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.4085272054999904</v>
+        <v>0.2992483126634391</v>
       </c>
     </row>
     <row r="3">
@@ -529,29 +529,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09175064602217944</v>
+        <v>-0.1873410609940913</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3985929367929661</v>
+        <v>0.2320883260012899</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2821475818491996</v>
+        <v>0.1688818575596725</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1738404933117715</v>
+        <v>-0.1642790312217153</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2723087189757031</v>
+        <v>-0.05378421854313662</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.09160246072020352</v>
+        <v>-0.03980940402947117</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.693553679011008</v>
+        <v>0.535828782289284</v>
       </c>
     </row>
   </sheetData>
